--- a/docs/QA_Test_Cases.xlsx
+++ b/docs/QA_Test_Cases.xlsx
@@ -15,14 +15,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Negative Cases" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Cases" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Auth &amp; RBAC'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Business Unit'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Single Screening'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Batch Screening'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scheduled Screening'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Results Dashboard'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'User Administration'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily Schedule Admin'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Audit &amp; Ops Controls'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Negative Cases'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Stress Cases'!$A$1:$D$26</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +42,22 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,8 +72,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,448 +484,455 @@
   </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>AUTH-001 - Sign-in page appears for unauthenticated user</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Set VITE_AUTH_ENABLED=true; clear browser session; open the application root URL.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>User sees the Sign in required screen and cannot access screening forms until login.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>AUTH-002 - Successful OIDC login loads application shell</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Login with a valid OIDC user from the identity provider.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Application loads with top navigation, user identity details, and screening workspace.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AUTH-003 - Sign out button ends active session</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Login; click Sign Out from header.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Session is removed and user is redirected to signed-out flow.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>AUTH-004 - Signed-out page supports re-login</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>After sign-out, click Sign In Again on signed-out page.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>User is redirected to identity provider login and can authenticate again.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>AUTH-005 - Idle timeout auto logout</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Set VITE_OIDC_IDLE_TIMEOUT_MS to a short value; login; remain idle beyond timeout.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>User is automatically logged out and redirected to signed-out experience.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>AUTH-006 - Authentication error screen can retry</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Force auth callback failure or invalid auth state; open app.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Authentication Error card is shown and Retry Sign In starts sign-in redirect.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>AUTH-007 - Missing bearer token returns 401</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Call any /api/v1 endpoint without Authorization header when AUTH_ENABLED=true.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 and request is denied.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>AUTH-008 - Invalid or expired bearer token returns 401</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Call any /api/v1 endpoint with malformed or expired bearer token.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 with token validation error detail.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>AUTH-009 - Audience mismatch token is rejected</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Use token whose aud, client_id, and azp do not match AUTH_AUDIENCE.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 and does not execute the protected action.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>AUTH-010 - Auth disabled mode grants local admin principal</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Set AUTH_ENABLED=false and VITE_AUTH_ENABLED=false; open app and call APIs.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>App loads without OIDC challenge; protected APIs are accessible as local dev admin principal.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RBAC-001 - Viewer can access single screening in mock mode</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Login as viewer-role user and open Screening tab.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Single screening form is available with mock-only behavior.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>RBAC-002 - Viewer cannot run non-mock single screening</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Login as viewer; attempt to disable mock option and submit.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UI prevents non-mock submit and shows viewer mock-only restriction.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>RBAC-003 - Viewer cannot access batch screening actions</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Login as viewer and inspect tabs and controls.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Batch tab is disabled or inaccessible for viewer.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>RBAC-004 - Viewer cannot access scheduled screening actions</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Login as viewer and inspect schedule tab.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Schedule tab is disabled or inaccessible for viewer.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>RBAC-005 - Analyst can run single screening with mock off</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Login as analyst; submit single screening with mock unchecked.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Request is accepted and returns screening response.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>RBAC-006 - Analyst can run batch screening</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Login as analyst; submit valid batch file.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Batch job is accepted and appears in results.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>RBAC-008 - Compliance can configure scheduled screening</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Login as compliance; submit schedule from Schedule tab.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Schedule is created and daily_schedule_id is returned.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>RBAC-010 - Useradmin can access user administration</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Login as useradmin role; open /manage-users route.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>User administration page loads with BU and mapping controls.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>RBAC-012 - Admin can access all admin areas</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Login as admin; open User Administration, Daily Schedule, and Audit Log routes.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>All admin/compliance pages are accessible and functional.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -909,1132 +943,1183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>NEG-ADM-001 - Save BU mapping without selected user is blocked</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>On Manage Users page clear selected user and click Save Mapping.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UI shows Select a user to map Business Units error.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>NEG-ADM-002 - Unauthorized user cannot update BU mappings</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Call PUT /api/v1/admin/business-unit-mappings/{user_id} without admin/useradmin scope.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 insufficient scope.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-001 - Sensitive query params must be masked in access logs</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Invoke API with query params token,password,secret,email and inspect api_access_logs.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Logged query string is masked/redacted and raw secrets are not stored.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-002 - 401 auth failures are auditable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Trigger 401 on /api/v1 endpoint and inspect audit_events.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>API_AUTHENTICATION_FAILED audit event is present with correlation id.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-003 - 403 authorization failures are auditable</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Trigger 403 on protected endpoint and inspect audit_events.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>API_AUTHORIZATION_FAILED audit event is present with correlation id.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-004 - High-risk API failure alert is deduplicated within window</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Generate failures above threshold multiple times within same alert window.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Only first alert in window is new; subsequent checks do not duplicate alert event.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-005 - Retention cleanup deletes only records older than cutoff</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Seed old and recent operational rows then run cleanup cycle.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Only rows older than retention period are purged.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-006 - SNS publish failure writes audit event</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Configure failing SNS publish path for schedule notification.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>SNS_NOTIFICATION_PUBLISH_FAILED event is logged with failure details.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-007 - Malformed SQS message is audited and removed</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Push invalid message body to screening queue for worker consumption.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Worker logs SQS_MESSAGE_DECODE_FAILED and deletes malformed message.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>NEG-AUD-008 - Raw API troubleshooting logs must redact secrets when enabled</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Enable ACTIMIZE_LOG_RAW_API_IO, execute screening, and inspect emitted application logs.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Logged payloads redact bearer tokens, client secrets, client assertions, and similar sensitive values.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>NEG-AUTH-001 - Missing bearer token is rejected</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Call any /api/v1 endpoint without Authorization header when AUTH_ENABLED=true.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 and request is denied.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NEG-AUTH-002 - Expired access token is rejected</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Call /api/v1 endpoint using expired JWT token.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 with token validation failure.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>NEG-AUTH-003 - Tampered token signature is rejected</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Modify JWT payload/signature and call protected API.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 401 and does not process request.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>NEG-AUTH-004 - Auth enabled without issuer/jwks fails</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Set AUTH_ENABLED=true but leave AUTH_ISSUER or AUTH_JWKS_URL empty; call protected endpoint.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 500 with auth configuration error.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-001 - Unsupported upload extension is rejected by batch-upload API</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>POST batch-upload using .xls or .txt file name and multipart body.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 Only CSV or XLSX files are allowed.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-002 - Non-array screening_types_json is rejected</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>POST batch-upload with screening_types_json as object/string instead of array.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 screening_types_json must be a JSON array.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-003 - Missing upload file is rejected</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>POST batch-upload without file form part.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 file is required.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-004 - Empty upload file is rejected</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>POST batch-upload with zero-byte file.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 Uploaded file is empty.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-005 - Duplicate PartyKey in upload is rejected</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Upload batch with duplicate PartyKey values.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 Upload validation failed with duplicate PartyKey detail.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-006 - Header-only upload is rejected</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Upload CSV/XLSX containing headers only and no data rows.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 No rows found in the file.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-007 - Individual row missing required names is rejected</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Upload Individual row without Full Name and without First Name + Last Name.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 with Individual naming validation detail.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-008 - Invalid gender value in upload is rejected</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Upload row with gender value outside Male, Female, Other, or blank.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 gender validation error.</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-009 - Organization or Unknown row missing full name is rejected</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Upload Organization or Unknown row with blank Full Name.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 with Full Name required validation detail.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-010 - Large immediate batch fails when S3 dispatch unavailable</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Submit immediate batch when AWS_S3_UPLOAD_BUCKET is not configured.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 500 requiring S3 storage for batch dispatch.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-011 - Unknown job id polling returns 404</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Call GET /api/v1/screenings/jobs/{unknown_job_id}.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 404 Job not found.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>NEG-BAT-012 - Corrupt queries.json in JOB_DISPATCH fails job</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Corrupt uploaded queries.json in S3 before worker dispatch processing.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Worker marks job FAILED and logs BATCH_DISPATCH_FAILED audit event.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>NEG-BU-001 - Single screening without BU is rejected</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>POST /api/v1/screenings/match with missing business_unit_code.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 Business Unit is required.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>NEG-BU-002 - Single screening with unmapped BU is rejected</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>POST /api/v1/screenings/match using business_unit_code not mapped to caller.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 and no screening is executed.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>NEG-BU-003 - Batch upload with unmapped BU is rejected</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>POST /api/v1/screenings/batch-upload using unmapped business_unit_code.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 and batch job is not queued.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>NEG-BU-004 - Create business unit with blank code fails</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Call POST /api/v1/admin/business-units with empty business_unit_code.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 Business Unit code is required.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>NEG-BU-005 - Update BU to duplicate code fails</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Call PUT /api/v1/admin/business-units/{code} with next code already existing.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 duplicate business unit code error.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NEG-BU-006 - Delete unknown BU returns not found</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Call DELETE /api/v1/admin/business-units/{unknown_code}.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>API returns HTTP 404 Business Unit not found.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>NEG-BU-006 - Screening type request blocks unmapped Business Unit</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Call GET /api/v1/screenings/types?business_unit_code=&lt;unmapped&gt; as a user without that BU mapping.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>API rejects request and does not return Business Unit-specific screening options.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEG-DLY-001 - Unauthorized user cannot remove daily schedule</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Call DELETE /api/v1/screenings/daily-schedules/{id} without screening.daily/admin permission.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>NEG-DLY-001 - Schedule page below one is rejected by validation</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Call GET /api/v1/screenings/daily-schedules?page=0.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI query validation rejects the request because page must be &gt;= 1.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>NEG-DLY-002 - Batch run page below one is rejected by validation</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Call GET /api/v1/screenings/daily-schedules/batch-runs?page=0 as admin.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI query validation rejects the request because page must be &gt;= 1.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>NEG-RBAC-001 - Viewer cannot call batch create API</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Login as viewer and call POST /api/v1/screenings/jobs.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 insufficient scope.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEG-DLY-002 - Daily schedule list API failure is surfaced</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Force /screenings/daily-schedules API failure and open Daily Schedule page.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>UI shows Failed to load daily schedules error state.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEG-RBAC-001 - Viewer cannot call batch create API</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Login as viewer and call POST /api/v1/screenings/jobs.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>NEG-RBAC-002 - Analyst cannot disable daily schedules</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Login as analyst and call DELETE /api/v1/screenings/daily-schedules/{schedule_id}.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 insufficient scope.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEG-RBAC-002 - Analyst cannot disable daily schedules</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Login as analyst and call DELETE /api/v1/screenings/daily-schedules/{schedule_id}.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>NEG-RBAC-003 - Analyst cannot read audit events</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Login as analyst and call GET /api/v1/audit-events.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 insufficient scope.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEG-RBAC-003 - Analyst cannot read audit events</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Login as analyst and call GET /api/v1/audit-events.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>API returns HTTP 403 insufficient scope.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>NEG-RES-001 - Summary API failure shows error banner</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Force /screenings/summary API failure and load Screening page.</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UI shows failed-to-load summary error state.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>NEG-RES-002 - Recent results API failure shows error banner</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Force /screenings/results API failure and load or refresh Screening page.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UI shows failed-to-load screening results error state.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>NEG-RES-003 - Failed row hit dialog shows failure details</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Open hit entity dialog on Failed result row.</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Dialog displays failure text and HTTP status when available.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-001 - Non-compliance cannot create scheduled screening</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Login as analyst/viewer and submit daily_screening=true request.</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>API/UI returns HTTP 403 scheduled screening not permitted.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-002 - Unknown schedule_id re-run request is rejected</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Call submit_job path with schedule_id that does not exist.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Request fails with 400 Daily schedule not found.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-003 - Subscribe API rejects empty email when principal email absent</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Call POST /screenings/daily-schedules/{id}/subscriptions with empty email and no user email claim.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 email is required.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-004 - Unsubscribe nonexistent subscription returns 404</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Call DELETE subscription endpoint for email not subscribed to schedule.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 404 Subscription not found.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-005 - Remove unknown schedule returns 404</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Call DELETE /screenings/daily-schedules/{unknown_schedule_id}.</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 404 Daily schedule not found.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>NEG-SCH-006 - Invalid schedule file type blocked in UI</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>In Schedule tab upload unsupported extension and submit.</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UI blocks submit with CSV/XLSX file type validation message.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>NEG-SNG-001 - Empty single query payload is rejected</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>POST /api/v1/screenings/match with queries={} .</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 400 At least one query is required.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>NEG-SNG-002 - Viewer non-mock single call is denied</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Login as viewer and call /screenings/match with mock_screening=false.</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>API returns HTTP 403 Viewer can perform only mock single screening.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>NEG-SNG-003 - Upstream screening failure normalizes failed response</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Force Actimize failure during single screening.</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Item response has status=500 and error text; audit and external error records are written.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>NEG-SNG-004 - Invalid DOB blocks submission in UI</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>In Single tab enter DOB in invalid format and submit.</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UI validation blocks submit with DOB format error.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>NEG-CBK-001 - Callback missing unique key is rejected</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Post Actimize callback without unique_key.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>API returns HTTP 400 with unique_key required and no callback row/item update is written.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>NEG-CBK-002 - Callback invalid status code is rejected</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Post Actimize callback with status_cd=P or another unsupported value.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>API returns HTTP 400 stating status_cd must be F or T.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2045,494 +2130,589 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STR-001 - Single screening concurrent load</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Run 50 concurrent single-screening requests for 10 minutes with mixed entities and screening types.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>System remains stable, no crashes, and p95 response latency stays within agreed SLA.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STR-002 - Immediate large batch submit under timeout window</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Submit a large immediate batch (for example 10k+ records) through batch-upload endpoint.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>API quickly returns accepted job response and does not time out at gateway/proxy layer.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STR-003 - Worker throughput at configured TPS cap</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Set SCREENING_TPS=32 and run sustained batch load for 30 minutes.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Outbound screening call rate is throttled near configured cap without uncontrolled spikes.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>STR-004 - Queue backlog drain test</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Create backlog of 100k queue items and run worker with configured parallelism.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Backlog drains steadily; worker does not deadlock; jobs eventually complete or fail cleanly.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>STR-005 - Parallel message processing saturation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Increase SCREENING_PARALLEL_MESSAGES and process high-volume batch traffic.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Throughput improves up to infrastructure limits without data corruption or duplicate final states.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>STR-006 - Multi-user concurrent batch submissions</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Simulate 20+ concurrent users each uploading batch files simultaneously.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>All submissions receive valid job IDs; no cross-user data leakage; system remains responsive.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>STR-007 - Polling load on job status endpoint</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Run 200+ concurrent clients polling /screenings/jobs/{job_id} at configured intervals.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Endpoint remains available with acceptable latency and correct progress counters.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>STR-008 - Midnight schedule burst execution</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Configure many schedules due at the same minute in America/New_York and run worker loop.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Schedules are claimed once each, jobs created without duplication, and next_run_at updates correctly.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>STR-009 - External API high-latency endurance</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Inject upstream screening latency (for example 5-10s) during sustained batch load.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Worker continues processing with controlled throughput and without queue consumer collapse.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>STR-010 - External API failure storm handling</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Force repeated upstream failures above high-risk threshold during a fixed time window.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Failures are recorded, high-risk alert is emitted, and worker continues processing remaining items.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>STR-011 - Operational cleanup on large tables</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Seed very large audit/access/error tables and trigger retention cleanup cycle.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Cleanup completes without service interruption and purges only records older than cutoff.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>STR-012 - Audit log UI with large dataset</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Load 50k+ audit events and navigate pages and filters in Audit Log UI.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Pagination and filtering remain usable without browser lockup or major rendering issues.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>STR-013 - Results table stress with large submissions</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Load submissions producing 20k+ result rows and test search, sort, and pagination.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Results interactions remain functional and state changes complete within acceptable time.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>STR-014 - CSV export with large filtered result set</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Export CSV from a large filtered dataset (for example 50k rows).</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Export completes successfully and file contains complete, correctly ordered data.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>STR-015 - Business unit mapping bulk administration</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Perform rapid updates for many user-to-BU mappings in admin APIs.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Mappings persist correctly, no partial corruption, and API remains stable under burst writes.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>STR-016 - Schedule subscription fan-out load</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Subscribe many recipients across multiple schedules and trigger completion notifications.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Subscription persistence remains consistent and notification publishing does not block job completion.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>STR-017 - Worker restart during heavy processing</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Restart worker process repeatedly while high-volume jobs are in progress.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Processing resumes safely, no permanent stuck jobs, and queue messages are eventually reconciled.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>STR-018 - Duplicate message delivery resilience</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Simulate SQS duplicate deliveries for same job item under load.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Idempotent updates prevent inconsistent final state and job counts remain accurate.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>STR-019 - Correlation-id traceability under high concurrency</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Generate high concurrent API, queue, and worker traffic with mixed correlation IDs.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Each request path remains traceable end-to-end across access logs, audit events, and error records.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>STR-020 - End-to-end soak test</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Run continuous mixed workload (single, batch, schedule) for 24 hours.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>No memory leak or progressive degradation; error rate and latency remain within acceptable threshold.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>STR-021 - 20-user shared-file batch benchmark captures timeout behavior</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Run the retained 20-user same-file batch benchmark against deployed CloudFront using the current performance script.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Benchmark output records success count, latency percentiles, and any CloudFront timeout count for regression comparison.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>STR-022 - Daily schedule pagination under high schedule count</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Seed hundreds of active schedules and repeatedly page through /daily-schedules as compliance/admin.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Responses remain bounded to 10 schedule items per page and page metadata remains accurate under load.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>STR-023 - Batch run status pagination under high run count</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Seed thousands of scheduled/ad-hoc runs and page through /daily-schedules/batch-runs as admin.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Responses remain bounded to 50 run rows per page and query latency stays within agreed admin-page SLA.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>STR-024 - Worker delayed retry storm remains controlled</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Force transient Actimize failures for many queued SCREEN_ITEM messages.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Worker requeues within max attempts using bounded delays and does not exceed configured TPS or duplicate completed items.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>STR-025 - Split queue dispatcher large batch soak</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Run sustained large batch submissions with split dispatch/screening queues for at least 30 minutes.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch queue remains bounded, screening queue drains steadily, and dispatcher/worker health endpoints remain healthy.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2543,252 +2723,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>BU-001 - User mapped business units load in screening page</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Login with mapped user; open Screening page.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Business Unit dropdown is populated with active mapped units.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>BU-002 - Business unit defaults to first available option</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Login with multiple mapped units; load Screening page fresh.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Single, Batch, and Schedule forms auto-select a valid BU option.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BU-003 - No mapped BU shows blocking warning</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Login with user not mapped to active BUs; open Screening page.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Warning indicates no mapped BU and screening submission is blocked.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BU-004 - Single screening requires business unit</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Clear BU selection in Single tab and submit.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Validation error states Business Unit is required.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>BU-005 - Batch screening requires business unit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Clear BU selection in Batch tab and submit.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Validation error states Business Unit is required.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BU-006 - Scheduled screening requires business unit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Clear BU selection in Schedule tab and submit.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Validation error states Business Unit is required.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>BU-007 - Screening page excludes inactive or unmapped business units</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Deactivate one business unit or remove the user mapping, then reload the Screening page.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Business Unit dropdown excludes inactive or unmapped options.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>BU-008 - Updated user-to-business-unit mapping is reflected on screening page</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Save a revised BU mapping for a user, then reload the Screening page for that user.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Available Business Unit options reflect the updated mapping.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BU-009 - Business unit code normalization is uppercase</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Submit lowercase business_unit_code in API payload.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Stored metadata and response expose normalized uppercase BU code.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>BU-010 - Fallback BU applies only when user has no mappings</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Use user with zero mappings and submit default fallback BU; then use user with mappings and same BU.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Fallback BU works only for unmapped user; mapped user is validated strictly.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BU-011 - Screening type options are scoped by selected Business Unit</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Login with a user mapped to multiple Business Units; switch Business Unit selection and call GET /api/v1/screenings/types?business_unit_code=&lt;code&gt;.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>API returns only active screening type options allowed for the selected Business Unit; UI refreshes the checkbox list without stale options.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BU-012 - Screening type options reject unmapped Business Unit</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Login as a user not mapped to a target Business Unit and call GET /api/v1/screenings/types?business_unit_code=&lt;unmapped&gt;.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>API returns an authorization/validation error and does not disclose options for the unmapped Business Unit.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BU-013 - Business Unit rename keeps related mappings usable</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>As admin, rename an existing Business Unit code, then load user mappings and submit a screening with the renamed code.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Related user mappings and job metadata references are updated consistently; screening accepts the renamed active Business Unit.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2799,340 +3052,391 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SNG-001 - Single screening success for Individual split name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Enter first and last name for Individual; select at least one screening type; submit.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Result row is created with Single mode and clear or potential match status.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SNG-002 - Single screening success for Individual full name only</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Enter only full name for Individual and submit.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Submission succeeds and response is returned.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SNG-003 - Single screening success for Organization</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Set entity type Organization; provide full name; submit.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Submission succeeds and row appears in results.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SNG-004 - Single screening success for Vessel</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Set entity type Vessel; provide full name; submit.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Submission succeeds with Vessel entity type reflected in results.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SNG-005 - Validation blocks Individual without required name</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>For Individual, leave full name empty and do not provide first+last; submit.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Validation message indicates required naming rule for Individual.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SNG-006 - Validation blocks non-Individual without full name</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Set entity type Organization, Unknown, Vessel, or Aircraft with empty full name; submit.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Validation message indicates Name is required.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SNG-007 - DOB format validation</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Enter invalid DOB format for Individual and submit.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates DOB must be valid YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SNG-008 - DOB future date validation</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Enter a future DOB for Individual and submit.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates DOB cannot be in the future.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>SNG-009 - DOB older than 100 years validation</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Enter DOB older than 100 years and submit.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates DOB cannot be more than 100 years old.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SNG-010 - Single requires at least one screening type</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Deselect all screening types in Single tab and submit.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates at least one screening type is required.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SNG-011 - Alias entries are merged into submitted query</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Add multiple aliases using plus action and submit single screening.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Submitted query contains merged alias/name variants; screening executes once.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SNG-012 - Unsupported alias types do not allow extra name blocks</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Set entity type Vessel or Aircraft and attempt to add alias/name blocks.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Additional alias/name rows are not added for unsupported entity types.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SNG-013 - Multiple screening types execute in one single submit</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Select several screening types and submit one single request.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Response includes results for selected types within one business response.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SNG-014 - Single screening API failure is shown as failed row</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Force upstream screening failure for single screening.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Result row is marked Failed and hit detail dialog shows failure text.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SNG-015 - Single screening sends selected Business Unit to Actimize payload</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Submit a non-mock single screening with a mapped Business Unit and inspect redacted upstream payload/log or captured mock payload.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Actimize request includes businessUnit equal to the selected Business Unit code.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SNG-016 - Screening type list refreshes after Business Unit change</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Open Single tab, select Business Unit A, note available screening types, then select Business Unit B.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Available screening type options update from /screenings/types?business_unit_code=... and selected invalid types are cleared or blocked.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3143,450 +3447,567 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>BAT-001 - Batch upload accepts valid CSV template</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>In Batch tab, upload valid CSV with unique PartyKey and required names; submit.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Batch job accepted with job_id and placeholder rows shown as processing.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>BAT-002 - Batch upload accepts valid XLSX template</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Upload valid XLSX template file in Batch tab and submit.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Batch job accepted and visible in Screening Results.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BAT-003 - Batch upload rejects unsupported file extension</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Attempt upload of non-CSV/XLSX file and submit.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UI or API shows Only CSV or XLSX files are allowed.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BAT-004 - Batch upload requires a file selection</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Keep file empty and click Run Batch Screening.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UI shows Please drop or select a CSV or XLSX file.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>BAT-005 - Batch upload UI blocks oversized file above limit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Upload file larger than configured UI cap and submit.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UI blocks submission and shows max upload size message.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>BAT-006 - Batch upload rejects file with no data rows</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Upload file with headers but no data rows and submit.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Backend validation returns No rows found in the file.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>BAT-007 - Batch validation enforces PartyKey presence</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Upload file where one or more rows have blank PartyKey.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Validation error lists row numbers with PartyKey required.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>BAT-008 - Batch validation enforces PartyKey uniqueness</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Upload file containing duplicate PartyKey values.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates duplicate PartyKey in file.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BAT-009 - Batch validation enforces allowed gender code</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Upload row with gender value not M, F, or blank.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates gender code rule.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>BAT-010 - Batch validation enforces Individual naming rule</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Upload Individual row missing both Full Name and First Name + Last Name.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates that Individual requires either Full Name or both First Name and Last Name.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>BAT-011 - Batch validation enforces Organization or Unknown full name rule</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Upload Organization or Unknown row with blank Full Name.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates Full Name is required for Organization or Unknown.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>BAT-012 - Batch submit requires Batch Name</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Leave Batch Name empty and submit valid file.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UI shows Batch Name is required.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>BAT-013 - Batch submit requires at least one screening type</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Deselect all screening types and submit valid file.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UI shows Select at least one screening type.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>BAT-014 - Batch completion refresh updates item-level outcomes</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Submit valid batch and wait until job terminal state.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Items transition from Processing to Hit, No Hit, or Error and overall result is updated.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>BAT-015 - Batch timeout or failure marks pending rows as error</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Simulate long-running job timeout or processing failure.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Previously Processing rows are marked Error with failure message.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>BAT-016 - Immediate large batch path requires S3 dispatch storage</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Disable AWS_S3_UPLOAD_BUCKET and submit immediate batch upload.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>API returns server error indicating dispatch requires S3 storage.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>BAT-017 - Accepted batch response returns row metadata for placeholder rendering</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Submit valid batch file and inspect accepted response or initial UI placeholder rows.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Accepted result includes row-level metadata so placeholder rows show PartyKey/display name/entity type before completion.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>BAT-018 - Large immediate batch returns queued response before worker completion</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Submit large batch file with S3 dispatch enabled.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Response returns queued job details promptly while worker-side item expansion and screening continue asynchronously.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>BAT-019 - Header normalization tolerates case and separator variants</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Upload CSV/XLSX using equivalent headers such as Party Key, party_key, and PartyKey.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Backend parser maps equivalent headers successfully and submission is accepted.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>BAT-020 - Backend parsed upload returns row metadata</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Upload a valid CSV/XLSX batch and inspect POST /api/v1/screenings/batch-upload response.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Response includes row_meta entries with key, display_name, and ui_type for each accepted row.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BAT-021 - Large immediate batch uses JOB_DISPATCH path</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>With S3 upload bucket enabled, submit a large immediate batch such as 10k+ records.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>API returns quickly with accepted job; S3 contains source/query payload metadata and SQS receives a JOB_DISPATCH control message.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>BAT-022 - Worker expands JOB_DISPATCH into SCREEN_ITEM tasks</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>After BAT-021, run worker and monitor job_items plus SQS sends.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Worker downloads queries payload, creates item rows in bulk, and sends per-record SCREEN_ITEM messages in batches.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BAT-023 - Upload metadata captures source file hash and S3 path</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Submit a valid batch with S3 enabled and inspect batch_file_uploads.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Upload row stores file_hash, file_name, source S3 location, query payload location when generated, record_count, and user reference.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>BAT-024 - Split dispatch queue sends screen items to screening queue</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Configure different AWS_DISPATCH_SQS_QUEUE_NAME and AWS_SCREENING_SQS_QUEUE_NAME; submit a large immediate batch.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Backend enqueues JOB_DISPATCH to dispatch queue; dispatcher expands work and sends SCREEN_ITEM messages to the screening queue only.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3597,384 +4018,501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SCH-001 - Scheduled screening creation succeeds for compliance role</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Login as compliance or admin; complete Schedule tab required fields; submit.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Schedule is created, response includes daily_schedule_id, and results entry is added.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SCH-002 - Scheduled screening blocked for non-compliance role</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Login as analyst or viewer and attempt scheduled submit.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UI or API blocks schedule creation with permission error.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SCH-003 - Schedule Name is mandatory</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Leave Schedule Name blank and submit schedule.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates Schedule Name is required.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SCH-004 - Schedule requires at least one screening type</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Deselect all screening types in Schedule tab and submit.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates at least one screening type is required.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SCH-005 - Schedule requires Business Unit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Leave Schedule BU empty and submit.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates Business Unit is required.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SCH-006 - Schedule requires first run date and time</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Clear first run date/time and submit.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates run date/time is required.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SCH-007 - Schedule run date invalid format is rejected</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Enter invalid date/time value and submit schedule.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates run date/time is invalid.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SCH-008 - Schedule requires CSV or XLSX file</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Submit schedule without file.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Validation error indicates file is required.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>SCH-009 - Schedule subscription emails parse and deduplicate</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Enter repeated emails using comma, semicolon, and newline separators; submit.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Only unique normalized emails are subscribed.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SCH-010 - Daily frequency schedule uses configured cadence</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Create schedule with DAILY frequency and valid start.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Next run is calculated and schedule remains active.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SCH-011 - Weekly frequency schedule uses 7-day cadence</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Create schedule with WEEKLY frequency and inspect next_run_at progression.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Next run advances weekly in configured timezone.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SCH-012 - Monthly frequency schedule handles month boundaries</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Create MONTHLY schedule near end of month and trigger next cycle.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Next run adjusts correctly for shorter months.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SCH-013 - Deferred schedule start message shown when total_items=0</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Create schedule that is accepted with total_items=0 and daily_schedule_id present.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Result entry shows scheduled/deferred message instead of immediate processing.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SCH-014 - Re-upload for existing schedule screens only net-new records</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Submit follow-up scheduled file containing old and new records for same schedule.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Previously screened records are skipped and only net-new records are screened.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SCH-015 - Schedule subscriptions can be listed after creation</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Create schedule with one or more subscription emails, then reload subscription list.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Active subscriptions show normalized unique recipient emails for the schedule.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SCH-016 - Schedule subscription removal keeps remaining recipients active</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Remove one subscribed email from a schedule that has multiple recipients.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Removed email is no longer listed and remaining active subscriptions stay intact.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SCH-017 - Schedule list API returns paged response shape</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Create more than 10 active schedules and call GET /api/v1/screenings/daily-schedules?page=1.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Response has items, total, page, page_size=10, and total_pages; only the first page of active schedules is returned.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SCH-018 - Schedule completion subscription succeeds for allowed email</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>For an active schedule, call POST /api/v1/screenings/daily-schedules/{schedule_id}/subscriptions with an allowed email or use principal email.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Subscription is stored/updated, audit event is written, and SNS sync is attempted when notifications are enabled.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SCH-019 - Schedule subscription rejects disallowed email domain</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Call schedule subscription endpoint with an email outside the allowed domain.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>API returns HTTP 400 and does not create schedule_subscriptions or SNS subscription records.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SCH-020 - Scheduled upload preserves source upload id</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Create a scheduled batch through file upload and inspect response plus daily_schedules.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>daily_schedule_id and source_upload_id are returned; schedule row stores source file name, S3 URI when enabled, and Business Unit code.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SCH-021 - Ad-hoc rerun uses stored schedule source and owner</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Trigger POST /api/v1/screenings/daily-schedules/{schedule_id}/rerun for an active schedule.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>New queued job is accepted, associated to the schedule, uses stored source_upload_id/query source, and writes DAILY_SCHEDULE_ADHOC_RERUN_TRIGGERED audit event.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3985,318 +4523,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RES-001 - Dashboard summary counters match full-history statuses</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Create historical and recent submissions across clear, potential match, pending, failed, and match states.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Summary cards show accurate full-history totals per status even when the visible results grid is limited to recent rows.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RES-002 - Status filter narrows displayed rows</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Apply each status filter option on Screening Results table.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Only rows matching selected status are shown.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>RES-003 - Type filter narrows displayed rows by entity type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Apply type filter for Individual, Organization, Vessel, and Aircraft.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Only selected entity type rows remain visible.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RES-004 - Search filter matches key table fields</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Search by entity name, PartyKey, mode, type, or country.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Matching rows are returned and non-matching rows are hidden.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>RES-005 - Sorting by submitted date works both directions</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Toggle Submitted At sort from desc to asc and back.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Rows reorder correctly by timestamp.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>RES-006 - Sorting by status and score works</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Sort by Status and then Matching Score.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Rows follow configured rank logic for status and numeric order for score.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RES-007 - Pagination controls navigate full result set</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Load more rows than one page and use Next and Previous controls.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Page navigation updates row window without data loss.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RES-008 - Manual refresh reloads summary cards and recent results</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Click Refresh Results after new job activity.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Summary cards and the recent results table both reload from backend data and Last refreshed timestamp updates.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RES-009 - Auto-refresh runs while pending items exist</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Create job with pending rows and wait at least one refresh interval.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Pending entries auto-refresh until terminal states are reached.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>RES-010 - Export filtered results CSV contains visible dataset</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Apply filters then click Download Results CSV.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Downloaded CSV includes expected headers and only filtered rows.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RES-011 - Recent results grid loads newest rows while preserving full-history summary</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Create more than 300 results for one user and load the Screening page.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Summary cards reflect full history while the grid renders the newest recent-result window for responsiveness.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>RES-012 - Recent results API respects capped limit and newest-first ordering</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Call or exercise the recent results load with more than 300 available user rows.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Grid loads at most 300 rows ordered newest-first.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>RES-013 - Review alert link appears when Actimize review URL is configured</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Set VITE_ACTIMIZE_REVIEW_ALERT_URL and open hit entity details for a reviewable result.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Hit entity details show Open Actimize link pointing to the configured review URL.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RES-014 - Recent result rows include Business Unit and schedule activity metadata</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Run single, batch, and scheduled screenings; open Screening Results and inspect API rows.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Rows include businessUnitCode where available, dailyScheduleId for scheduled rows, and dailyScheduleActive state for active/inactive schedules.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RES-015 - Screening type labels are canonicalized from active mappings</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Configure active Actimize screening type mappings, run screenings with mapped source values, and load results.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Result rows display/group by canonical screening type labels from active mapping records rather than raw variant values.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4309,206 +4898,213 @@
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ADM-001 - Manage Users page denies unauthorized roles</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Login as non-admin non-useradmin and open /manage-users.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Access Denied screen is displayed.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ADM-002 - Create business unit with valid code and name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>As admin or useradmin, create new BU from User Administration page.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Business unit is saved, listed, and auditable.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ADM-003 - Business unit create/update requires code and name</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Attempt save with blank code or blank name.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UI shows validation error and save is blocked.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ADM-004 - Updating BU to duplicate code is blocked</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Edit BU and set next code equal to an existing BU code.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>API/UI returns error that duplicate code already exists.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ADM-005 - Deleting business unit removes it from selectable lists</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Delete an existing BU and refresh screening form dropdowns.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Deleted BU is absent from active options and mappings.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ADM-006 - Save user to business unit mapping persists selected codes</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Select user, choose multiple BUs, and click Save Mapping.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Saved mapping reflects selected BU codes on reload.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ADM-007 - Updating business unit code cascades to related mappings</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>As admin or useradmin, change a BU code that is already used by mappings or metadata.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Updated BU code is reflected in related admin and screening views without orphaned references.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>ADM-008 - Inactive business unit is excluded from screening dropdowns</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Mark a BU inactive or delete it, then reload screening forms.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Inactive BU no longer appears in screening dropdowns or active mapping selections.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4519,120 +5115,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DLY-001 - Daily Schedule admin page denies unauthorized user</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Login as role without screening.daily or screening.admin and open /daily-schedules.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Access Denied screen is displayed.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DLY-002 - Daily Schedule admin lists active schedules</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Login as compliance/admin and open Daily Schedule page.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Active schedules table loads with batch, frequency, and next run details.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DLY-002 - Daily Schedule admin lists active schedules with pagination</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Login as compliance/admin, create more than 10 active schedules, and open /daily-schedules.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Active schedules table loads first 10 records with total count, page count, Scheduled By, source file, frequency, next run, and actions.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>DLY-003 - Removing schedule deactivates only selected schedule</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>From Daily Schedule page click Remove for one schedule.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Selected schedule is removed from list while others remain.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>DLY-004 - Removing daily schedule is auditable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Remove a schedule from Daily Schedule admin page and inspect audit activity.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Schedule removal action is recorded in audit history with schedule identifier and actor.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DLY-005 - Daily Schedule page navigates schedule pages</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>On /daily-schedules use previous/next controls for the active schedules table.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Page changes call GET /screenings/daily-schedules?page=N and the range text/buttons update correctly.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DLY-006 - Admin batch run status is paged at 50 records</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Login as admin; create more than 50 scheduled/ad-hoc runs; open Daily Schedule admin run status section.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Batch run status table shows page metadata, 50 records per page, owner, source file, item counts, and derived run_status.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DLY-007 - Batch run status is admin-only</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Login as compliance user without screening.admin and call GET /api/v1/screenings/daily-schedules/batch-runs.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>API returns HTTP 403 and UI hides the all-user batch run status section.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DLY-008 - Ad-hoc rerun refreshes schedule and batch run views</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Click Re-run for an active schedule from /daily-schedules.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>UI shows accepted job id, reloads current schedule page, resets batch runs to page 1, and new run appears for admin.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>DLY-009 - Removing schedule reloads current page without stale row</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Remove an active schedule from a non-empty page.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Schedule is deactivated, current page reloads from backend, total count decreases, and removed row no longer appears.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4643,208 +5356,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test case description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Step to test</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Final Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>AUD-001 - Audit log page admin-only and data loads</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Login as admin; open Audit Log page and load events.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Audit events are shown with paging controls.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>AUD-002 - Audit log user filter and errors-only filter work</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Apply user filter then enable Show errors only.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Displayed events are constrained by selected user and error criteria.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>AUD-003 - API access log is written for every /api/v1 request</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Invoke representative /api/v1 endpoints and inspect api_access_logs.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Each request has method, path, status, latency, and correlation id entry.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>AUD-004 - Audit page supports paged retrieval and page-size changes</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Open Audit Log page, change Records per page, and navigate between pages.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Total count, page range text, and page navigation update using paged backend results.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>AUD-005 - Raw upstream API troubleshooting logs redact secrets when enabled</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Enable ACTIMIZE_LOG_RAW_API_IO and execute screening through sync or batch flow.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Request and response logs are written with sensitive values such as tokens and secrets redacted.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>AUD-006 - External API failures are persisted and high-risk alert can trigger</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Force repeated upstream screening failures above configured threshold/window.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>external_api_errors rows are created and HIGH_RISK_EXTERNAL_API_FAILURE_ALERT is emitted once per window.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>AUD-007 - Retention cleanup purges old operational data and audits purge</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Seed old audit/access/error records; run worker cleanup cycle.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Old records are deleted per retention config and OPERATIONAL_DATA_PURGED event is logged when deletions occur.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>AUD-008 - Schedule subscription create and remove actions are auditable</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Create and remove schedule subscriptions, then inspect audit history.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Audit events capture subscription add/remove actions with schedule and email context.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AUD-009 - Actimize alert callback records and applies review status</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Post valid callback payload with unique_key, alert_id, and status_cd F/T for an item that has matching party key.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Callback row is stored, matching job item response is updated with alert status fields, parsed status is recalculated, and audit event is written.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AUD-010 - Invalid Actimize callback payload is rejected</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Post callback payload missing unique_key/alert_id or with status_cd outside F/T.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>API returns HTTP 400 and no item response mutation is applied.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AUD-011 - Worker health endpoint reflects recent activity</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Start worker, call configured /health endpoint, then simulate heartbeat older than WORKER_HEALTH_MAX_AGE_S if possible.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Health endpoint returns 200 while recent activity exists and degraded status after stale heartbeat threshold.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AUD-012 - External API high-risk alert threshold emits audit event</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Generate external_api_errors above configured threshold within configured window and run worker cleanup/alert loop.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>High-risk external API failure audit event is emitted once for the threshold window with provider and operation context.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AUD-013 - Dispatcher forwards unexpected screen item from dispatch queue</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>With split queues configured, place a valid SCREEN_ITEM message on the dispatch queue and run worker_app.dispatcher.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dispatcher forwards the item to the screening queue, deletes the dispatch message, and writes DISPATCH_QUEUE_SCREEN_ITEM_FORWARDED audit event.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AUD-014 - Dispatcher rejects same queue configuration</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Set AWS_DISPATCH_SQS_QUEUE_NAME equal to AWS_SCREENING_SQS_QUEUE_NAME and start worker_app.dispatcher.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dispatcher startup fails with a clear configuration error requiring distinct queues.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>